--- a/data-raw/model_calculations/model_calculations.xlsx
+++ b/data-raw/model_calculations/model_calculations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sam/Documents/GitHub/data-pack-commons/data-raw/model_calculations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AB82FB-B310-E143-ABBB-15FFE75E9148}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF75D365-7A4E-B742-AD1E-69C0E0BCAE56}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="20540" activeTab="1" xr2:uid="{534AEB7A-72AD-754E-A1BC-F197B85E6149}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_required!$A$1:$AK$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">dimension_Item_sets!$A$1:$AH$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">dimension_Item_sets!$A$1:$AF$188</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4466" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4167" uniqueCount="802">
   <si>
     <t>PMTCT_STAT_ART</t>
   </si>
@@ -2042,194 +2042,6 @@
     <t>iu2PV9NpeSd</t>
   </si>
   <si>
-    <t>TX_NEW.N.TBRate</t>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>TB_ART, Numerator, New on ART, finer age/sex, FY19 Results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>] / [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>TX_NEW, finer age/sex, FY19 Results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
-    <t>TB_ART (N, DSD+TA, Age/Sex/NewExistingArt/HIVStatus)</t>
-  </si>
-  <si>
-    <t>TJjb1v6zbUH</t>
-  </si>
-  <si>
-    <t>TX_NEW.N.PMTCTRate</t>
-  </si>
-  <si>
-    <t>TX_NEW.N.PostANC1Rate</t>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>PMTCT_ART, Numerator, New on ART, finer age/sex, FY19 Results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>] / [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>TX_NEW, finer age/sex, FY19 Results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>HTS_TST (PMTCT Post ANC1), Positives, finer age/sex, FY19 Results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>] / [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>TX_NEW, finer age/sex, FY19 Results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
-    <t>TX_NEW.N.VMMCRate</t>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>VMMC_CIRC, Positives, finer age/sex, FY19 Results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>] / [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>TX_NEW, finer age/sex, FY19 Results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF24292E"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
-    <t>vWBWKmRWFAC</t>
-  </si>
-  <si>
-    <t>FY19 Results Analytic Indicators: PMTCT_ART (NewExistingART)</t>
-  </si>
-  <si>
     <t>bQhs5uRiSni</t>
   </si>
   <si>
@@ -2246,9 +2058,6 @@
   </si>
   <si>
     <t>TB_PREV (N, DSD+TA, Age/TherapyType/NewExistingArt/HIVStatus) TARGET already on art</t>
-  </si>
-  <si>
-    <t>10-50+.&lt;15/&gt;15.d.u</t>
   </si>
   <si>
     <t>ag</t>
@@ -2742,7 +2551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -2764,9 +2573,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3084,7 +2890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B5E70E-6A90-034D-92D2-04FEFE90502B}">
-  <dimension ref="A1:AK72"/>
+  <dimension ref="A1:AK68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -3099,6 +2905,7 @@
     <col min="21" max="21" width="46.83203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="46.83203125" customWidth="1"/>
     <col min="23" max="23" width="16" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10562,19 +10369,19 @@
     </row>
     <row r="67" spans="1:37" ht="18" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>668</v>
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
+        <v>671</v>
       </c>
       <c r="E67" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>142</v>
@@ -10583,16 +10390,16 @@
         <v>143</v>
       </c>
       <c r="H67" t="s">
-        <v>669</v>
-      </c>
-      <c r="I67" t="s">
-        <v>670</v>
+        <v>668</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>667</v>
       </c>
       <c r="J67" t="s">
-        <v>139</v>
+        <v>457</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>149</v>
+        <v>417</v>
       </c>
       <c r="L67" t="s">
         <v>145</v>
@@ -10600,7 +10407,7 @@
       <c r="M67" t="s">
         <v>143</v>
       </c>
-      <c r="N67" s="4" t="s">
+      <c r="N67" t="s">
         <v>391</v>
       </c>
       <c r="O67" t="s">
@@ -10624,20 +10431,20 @@
       <c r="U67" t="s">
         <v>143</v>
       </c>
-      <c r="V67" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="W67" s="16" t="s">
-        <v>660</v>
+      <c r="V67" t="s">
+        <v>143</v>
+      </c>
+      <c r="W67" t="s">
+        <v>143</v>
       </c>
       <c r="X67" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y67" s="9" t="s">
-        <v>657</v>
+        <v>143</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>143</v>
       </c>
       <c r="Z67" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AA67" t="s">
         <v>143</v>
@@ -10664,10 +10471,10 @@
         <v>143</v>
       </c>
       <c r="AI67" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
+        <v>143</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>143</v>
       </c>
       <c r="AK67" t="s">
         <v>143</v>
@@ -10675,19 +10482,19 @@
     </row>
     <row r="68" spans="1:37" ht="18" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C68" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>673</v>
+        <v>2</v>
+      </c>
+      <c r="D68" t="s">
+        <v>672</v>
       </c>
       <c r="E68" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>142</v>
@@ -10696,25 +10503,25 @@
         <v>143</v>
       </c>
       <c r="H68" t="s">
-        <v>678</v>
-      </c>
-      <c r="I68" t="s">
-        <v>677</v>
+        <v>668</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>667</v>
       </c>
       <c r="J68" t="s">
-        <v>139</v>
-      </c>
-      <c r="K68" t="s">
-        <v>140</v>
+        <v>457</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>417</v>
       </c>
       <c r="L68" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M68" t="s">
         <v>143</v>
       </c>
-      <c r="N68" s="4" t="s">
-        <v>391</v>
+      <c r="N68" t="s">
+        <v>390</v>
       </c>
       <c r="O68" t="s">
         <v>143</v>
@@ -10737,20 +10544,20 @@
       <c r="U68" t="s">
         <v>143</v>
       </c>
-      <c r="V68" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="W68" s="16" t="s">
-        <v>660</v>
+      <c r="V68" t="s">
+        <v>143</v>
+      </c>
+      <c r="W68" t="s">
+        <v>143</v>
       </c>
       <c r="X68" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y68" s="19" t="s">
-        <v>685</v>
+        <v>143</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>143</v>
       </c>
       <c r="Z68" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AA68" t="s">
         <v>143</v>
@@ -10777,464 +10584,12 @@
         <v>143</v>
       </c>
       <c r="AI68" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ68">
-        <v>0</v>
+        <v>143</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>143</v>
       </c>
       <c r="AK68" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>19</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>672</v>
-      </c>
-      <c r="C69" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H69" t="s">
-        <v>538</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="J69" t="s">
-        <v>139</v>
-      </c>
-      <c r="K69" t="s">
-        <v>140</v>
-      </c>
-      <c r="L69" t="s">
-        <v>141</v>
-      </c>
-      <c r="M69" t="s">
-        <v>143</v>
-      </c>
-      <c r="N69" t="s">
-        <v>570</v>
-      </c>
-      <c r="O69" t="s">
-        <v>143</v>
-      </c>
-      <c r="P69" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>143</v>
-      </c>
-      <c r="R69" t="s">
-        <v>143</v>
-      </c>
-      <c r="S69" t="s">
-        <v>143</v>
-      </c>
-      <c r="T69" t="s">
-        <v>143</v>
-      </c>
-      <c r="U69" t="s">
-        <v>143</v>
-      </c>
-      <c r="V69" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="W69" s="16" t="s">
-        <v>660</v>
-      </c>
-      <c r="X69" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y69" s="19" t="s">
-        <v>685</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AF69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AH69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI69" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ69">
-        <v>0</v>
-      </c>
-      <c r="AK69" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="70" spans="1:37" ht="18" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>19</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>675</v>
-      </c>
-      <c r="C70" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>676</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H70" t="s">
-        <v>538</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="J70" t="s">
-        <v>139</v>
-      </c>
-      <c r="K70" t="s">
-        <v>140</v>
-      </c>
-      <c r="L70" t="s">
-        <v>148</v>
-      </c>
-      <c r="M70" t="s">
-        <v>143</v>
-      </c>
-      <c r="N70" t="s">
-        <v>511</v>
-      </c>
-      <c r="O70" t="s">
-        <v>143</v>
-      </c>
-      <c r="P70" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>143</v>
-      </c>
-      <c r="R70" t="s">
-        <v>143</v>
-      </c>
-      <c r="S70" t="s">
-        <v>143</v>
-      </c>
-      <c r="T70" t="s">
-        <v>143</v>
-      </c>
-      <c r="U70" t="s">
-        <v>143</v>
-      </c>
-      <c r="V70" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="W70" s="16" t="s">
-        <v>660</v>
-      </c>
-      <c r="X70" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y70" s="19" t="s">
-        <v>685</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AF70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AH70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI70" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ70">
-        <v>0</v>
-      </c>
-      <c r="AK70" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="71" spans="1:37" ht="18" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>681</v>
-      </c>
-      <c r="C71" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" t="s">
-        <v>683</v>
-      </c>
-      <c r="E71" t="s">
-        <v>3</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H71" t="s">
-        <v>680</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="J71" t="s">
-        <v>457</v>
-      </c>
-      <c r="K71" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="L71" t="s">
-        <v>145</v>
-      </c>
-      <c r="M71" t="s">
-        <v>143</v>
-      </c>
-      <c r="N71" t="s">
-        <v>391</v>
-      </c>
-      <c r="O71" t="s">
-        <v>143</v>
-      </c>
-      <c r="P71" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>143</v>
-      </c>
-      <c r="R71" t="s">
-        <v>143</v>
-      </c>
-      <c r="S71" t="s">
-        <v>143</v>
-      </c>
-      <c r="T71" t="s">
-        <v>143</v>
-      </c>
-      <c r="U71" t="s">
-        <v>143</v>
-      </c>
-      <c r="V71" t="s">
-        <v>143</v>
-      </c>
-      <c r="W71" t="s">
-        <v>143</v>
-      </c>
-      <c r="X71" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>143</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AF71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AH71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ71" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK71" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="72" spans="1:37" ht="18" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>682</v>
-      </c>
-      <c r="C72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" t="s">
-        <v>684</v>
-      </c>
-      <c r="E72" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H72" t="s">
-        <v>680</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="J72" t="s">
-        <v>457</v>
-      </c>
-      <c r="K72" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="L72" t="s">
-        <v>145</v>
-      </c>
-      <c r="M72" t="s">
-        <v>143</v>
-      </c>
-      <c r="N72" t="s">
-        <v>390</v>
-      </c>
-      <c r="O72" t="s">
-        <v>143</v>
-      </c>
-      <c r="P72" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>143</v>
-      </c>
-      <c r="R72" t="s">
-        <v>143</v>
-      </c>
-      <c r="S72" t="s">
-        <v>143</v>
-      </c>
-      <c r="T72" t="s">
-        <v>143</v>
-      </c>
-      <c r="U72" t="s">
-        <v>143</v>
-      </c>
-      <c r="V72" t="s">
-        <v>143</v>
-      </c>
-      <c r="W72" t="s">
-        <v>143</v>
-      </c>
-      <c r="X72" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y72" t="s">
-        <v>143</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AF72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AH72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ72" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK72" t="s">
         <v>143</v>
       </c>
     </row>
@@ -11246,7 +10601,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60BEDA6B-3F7E-D547-BD9D-9083103169CB}">
-  <dimension ref="A1:AK200"/>
+  <dimension ref="A1:AI188"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -11262,10 +10617,9 @@
     <col min="11" max="13" width="12.33203125" customWidth="1"/>
     <col min="14" max="18" width="10.83203125" customWidth="1"/>
     <col min="19" max="19" width="13.5" customWidth="1"/>
-    <col min="21" max="22" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>221</v>
       </c>
@@ -11326,59 +10680,53 @@
       <c r="T1" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V1" s="19" t="s">
-        <v>685</v>
+      <c r="U1" t="s">
+        <v>216</v>
+      </c>
+      <c r="V1" t="s">
+        <v>145</v>
       </c>
       <c r="W1" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="X1" t="s">
-        <v>145</v>
+        <v>218</v>
       </c>
       <c r="Y1" t="s">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="Z1" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="AA1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AB1" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="AC1" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="AD1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AE1" t="s">
-        <v>281</v>
+        <v>379</v>
       </c>
       <c r="AF1" t="s">
-        <v>289</v>
+        <v>402</v>
       </c>
       <c r="AG1" t="s">
-        <v>379</v>
+        <v>673</v>
       </c>
       <c r="AH1" t="s">
-        <v>402</v>
+        <v>797</v>
       </c>
       <c r="AI1" t="s">
-        <v>686</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>810</v>
-      </c>
-      <c r="AK1" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>174</v>
       </c>
@@ -11407,7 +10755,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K2:AAD2)</f>
+        <f t="shared" ref="J2:J33" si="0">_xlfn.TEXTJOIN(";",1,K2:AAB2)</f>
         <v>&lt;2mo</v>
       </c>
       <c r="K2" s="9"/>
@@ -11418,13 +10766,11 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
       <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="AB2" t="s">
+      <c r="Z2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -11453,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K3:AAD3)</f>
+        <f t="shared" si="0"/>
         <v>2-12mo</v>
       </c>
       <c r="K3" s="9"/>
@@ -11464,13 +10810,11 @@
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="AC3" t="s">
+      <c r="AA3" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -11499,8 +10843,8 @@
         <v>1</v>
       </c>
       <c r="J4" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K4:AAD4)</f>
-        <v>&lt;1-50+;&lt;1-18+;&lt;1-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;&lt;1-18+</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>149</v>
@@ -11511,12 +10855,8 @@
       <c r="O4" t="s">
         <v>229</v>
       </c>
-      <c r="U4" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V4" s="9"/>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>174</v>
       </c>
@@ -11545,19 +10885,15 @@
         <v>0.25</v>
       </c>
       <c r="J5" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K5:AAD5)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U5" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V5" s="9"/>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -11586,11 +10922,11 @@
         <v>0.2</v>
       </c>
       <c r="J6" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K6:AAD6)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>174</v>
       </c>
@@ -11619,8 +10955,8 @@
         <v>1</v>
       </c>
       <c r="J7" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K7:AAD7)</f>
-        <v>&lt;1-50+;1-50+;&lt;1-18+;1-4;1-50+/&lt;5;&lt;1-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;1-50+;&lt;1-18+;1-4;1-50+/&lt;5</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>149</v>
@@ -11639,12 +10975,8 @@
       <c r="R7" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="U7" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V7" s="9"/>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>174</v>
       </c>
@@ -11673,8 +11005,8 @@
         <v>0.5</v>
       </c>
       <c r="J8" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K8:AAD8)</f>
-        <v>&lt;1-50+;1-50+;&lt;1-18+;1-4;1-50+/&lt;5;&lt;1-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;1-50+;&lt;1-18+;1-4;1-50+/&lt;5</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>149</v>
@@ -11693,12 +11025,8 @@
       <c r="R8" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="U8" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V8" s="9"/>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -11727,18 +11055,14 @@
         <v>0.25</v>
       </c>
       <c r="J9" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K9:AAD9)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P9" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U9" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V9" s="9"/>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>174</v>
       </c>
@@ -11767,7 +11091,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K10:AAD10)</f>
+        <f t="shared" si="0"/>
         <v>1-4;1-50+/&lt;5</v>
       </c>
       <c r="Q10" s="9" t="s">
@@ -11777,7 +11101,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -11806,8 +11130,8 @@
         <v>1</v>
       </c>
       <c r="J11" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K11:AAD11)</f>
-        <v>&lt;1-50+;1-50+;&lt;1-18+;1-50+/&lt;5;&lt;1-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;1-50+;&lt;1-18+;1-50+/&lt;5</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>149</v>
@@ -11823,12 +11147,8 @@
       <c r="R11" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="U11" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V11" s="9"/>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>174</v>
       </c>
@@ -11857,8 +11177,8 @@
         <v>0.5</v>
       </c>
       <c r="J12" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K12:AAD12)</f>
-        <v>&lt;1-50+;1-50+;&lt;1-18+;1-50+/&lt;5;&lt;1-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;1-50+;&lt;1-18+;1-50+/&lt;5</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>149</v>
@@ -11874,12 +11194,8 @@
       <c r="R12" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="U12" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V12" s="9"/>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>174</v>
       </c>
@@ -11908,18 +11224,14 @@
         <v>0.25</v>
       </c>
       <c r="J13" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K13:AAD13)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U13" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V13" s="9"/>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>174</v>
       </c>
@@ -11948,8 +11260,8 @@
         <v>1</v>
       </c>
       <c r="J14" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K14:AAD14)</f>
-        <v>&lt;1-50+;1-50+;10-50+;&lt;1-18+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;1-50+;10-50+;&lt;1-18+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>149</v>
@@ -11970,14 +11282,8 @@
       <c r="T14" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U14" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V14" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>174</v>
       </c>
@@ -12006,20 +11312,14 @@
         <v>0.25</v>
       </c>
       <c r="J15" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K15:AAD15)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P15" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U15" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V15" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>143</v>
       </c>
@@ -12048,7 +11348,7 @@
         <v>0.1111</v>
       </c>
       <c r="J16" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K16:AAD16)</f>
+        <f t="shared" si="0"/>
         <v>missing_age_1</v>
       </c>
       <c r="K16" s="4"/>
@@ -12061,7 +11361,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>174</v>
       </c>
@@ -12090,7 +11390,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K17:AAD17)</f>
+        <f t="shared" si="0"/>
         <v>&lt;15/&gt;15</v>
       </c>
       <c r="P17" s="9" t="s">
@@ -12099,7 +11399,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>143</v>
       </c>
@@ -12128,14 +11428,14 @@
         <v>0.5</v>
       </c>
       <c r="J18" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K18:AAD18)</f>
+        <f t="shared" si="0"/>
         <v>missing_age_2</v>
       </c>
       <c r="S18" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>174</v>
       </c>
@@ -12164,14 +11464,14 @@
         <v>1</v>
       </c>
       <c r="J19" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K19:AAD19)</f>
+        <f t="shared" si="0"/>
         <v>&lt;1-18+</v>
       </c>
       <c r="O19" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>174</v>
       </c>
@@ -12200,20 +11500,14 @@
         <v>0.125</v>
       </c>
       <c r="J20" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K20:AAD20)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P20" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U20" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V20" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>174</v>
       </c>
@@ -12242,8 +11536,8 @@
         <v>1</v>
       </c>
       <c r="J21" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K21:AAD21)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>149</v>
@@ -12263,14 +11557,8 @@
       <c r="T21" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U21" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V21" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -12299,7 +11587,7 @@
         <v>0.1111</v>
       </c>
       <c r="J22" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K22:AAD22)</f>
+        <f t="shared" si="0"/>
         <v>missing_age_1</v>
       </c>
       <c r="K22" s="4"/>
@@ -12312,7 +11600,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>174</v>
       </c>
@@ -12341,14 +11629,14 @@
         <v>1</v>
       </c>
       <c r="J23" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K23:AAD23)</f>
+        <f t="shared" si="0"/>
         <v>&lt;15/&gt;15</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>143</v>
       </c>
@@ -12377,7 +11665,7 @@
         <v>0.5</v>
       </c>
       <c r="J24" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K24:AAD24)</f>
+        <f t="shared" si="0"/>
         <v>missing_age_2</v>
       </c>
       <c r="K24" s="4"/>
@@ -12390,7 +11678,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>174</v>
       </c>
@@ -12419,7 +11707,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K25:AAD25)</f>
+        <f t="shared" si="0"/>
         <v>&lt;1-18+</v>
       </c>
       <c r="K25" s="5"/>
@@ -12431,7 +11719,7 @@
       </c>
       <c r="P25" s="5"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>174</v>
       </c>
@@ -12460,7 +11748,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K26:AAD26)</f>
+        <f t="shared" si="0"/>
         <v>&lt;1-18+</v>
       </c>
       <c r="K26" s="5"/>
@@ -12472,7 +11760,7 @@
       </c>
       <c r="P26" s="5"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>174</v>
       </c>
@@ -12501,20 +11789,14 @@
         <v>0.125</v>
       </c>
       <c r="J27" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K27:AAD27)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U27" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V27" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>174</v>
       </c>
@@ -12543,8 +11825,8 @@
         <v>1</v>
       </c>
       <c r="J28" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K28:AAD28)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>149</v>
@@ -12564,14 +11846,8 @@
       <c r="T28" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U28" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V28" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -12600,7 +11876,7 @@
         <v>0.1111</v>
       </c>
       <c r="J29" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K29:AAD29)</f>
+        <f t="shared" si="0"/>
         <v>missing_age_1</v>
       </c>
       <c r="K29" s="4"/>
@@ -12613,7 +11889,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>174</v>
       </c>
@@ -12642,20 +11918,14 @@
         <v>0.125</v>
       </c>
       <c r="J30" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K30:AAD30)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P30" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U30" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V30" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>174</v>
       </c>
@@ -12684,8 +11954,8 @@
         <v>1</v>
       </c>
       <c r="J31" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K31:AAD31)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f t="shared" si="0"/>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>149</v>
@@ -12707,14 +11977,8 @@
       <c r="T31" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U31" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V31" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>174</v>
       </c>
@@ -12743,14 +12007,14 @@
         <v>0.2</v>
       </c>
       <c r="J32" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K32:AAD32)</f>
+        <f t="shared" si="0"/>
         <v>10-50+.all</v>
       </c>
       <c r="T32" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -12779,7 +12043,7 @@
         <v>0.1111</v>
       </c>
       <c r="J33" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K33:AAD33)</f>
+        <f t="shared" si="0"/>
         <v>missing_age_1</v>
       </c>
       <c r="K33" s="4"/>
@@ -12792,7 +12056,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>174</v>
       </c>
@@ -12821,14 +12085,14 @@
         <v>1</v>
       </c>
       <c r="J34" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K34:AAD34)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K34:AAB34)</f>
         <v>&lt;1-18+</v>
       </c>
       <c r="O34" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>174</v>
       </c>
@@ -12857,20 +12121,14 @@
         <v>0.125</v>
       </c>
       <c r="J35" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K35:AAD35)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K35:AAB35)</f>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U35" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V35" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>174</v>
       </c>
@@ -12899,14 +12157,14 @@
         <v>0.2</v>
       </c>
       <c r="J36" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K36:AAD36)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K36:AAB36)</f>
         <v>10-50+.all</v>
       </c>
       <c r="T36" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>174</v>
       </c>
@@ -12935,8 +12193,8 @@
         <v>1</v>
       </c>
       <c r="J37" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K37:AAD37)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K37:AAB37)</f>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>149</v>
@@ -12958,14 +12216,8 @@
       <c r="T37" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U37" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V37" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -12994,7 +12246,7 @@
         <v>0.11119999999999999</v>
       </c>
       <c r="J38" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K38:AAD38)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K38:AAB38)</f>
         <v>missing_age_1</v>
       </c>
       <c r="K38" s="4"/>
@@ -13007,7 +12259,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>174</v>
       </c>
@@ -13036,20 +12288,14 @@
         <v>0.125</v>
       </c>
       <c r="J39" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K39:AAD39)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K39:AAB39)</f>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U39" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V39" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>174</v>
       </c>
@@ -13078,14 +12324,14 @@
         <v>0.2</v>
       </c>
       <c r="J40" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K40:AAD40)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K40:AAB40)</f>
         <v>10-50+.all</v>
       </c>
       <c r="T40" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>174</v>
       </c>
@@ -13114,8 +12360,8 @@
         <v>1</v>
       </c>
       <c r="J41" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K41:AAD41)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K41:AAB41)</f>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>149</v>
@@ -13135,14 +12381,8 @@
       <c r="T41" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U41" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V41" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -13171,7 +12411,7 @@
         <v>0.1111</v>
       </c>
       <c r="J42" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K42:AAD42)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K42:AAB42)</f>
         <v>missing_age_1</v>
       </c>
       <c r="K42" s="4"/>
@@ -13184,7 +12424,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>174</v>
       </c>
@@ -13213,8 +12453,8 @@
         <v>1</v>
       </c>
       <c r="J43" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K43:AAD43)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K43:AAB43)</f>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>149</v>
@@ -13234,14 +12474,8 @@
       <c r="T43" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U43" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V43" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>174</v>
       </c>
@@ -13270,20 +12504,14 @@
         <v>0.125</v>
       </c>
       <c r="J44" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K44:AAD44)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K44:AAB44)</f>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P44" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U44" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V44" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>174</v>
       </c>
@@ -13312,14 +12540,14 @@
         <v>0.2</v>
       </c>
       <c r="J45" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K45:AAD45)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K45:AAB45)</f>
         <v>10-50+.all</v>
       </c>
       <c r="T45" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>174</v>
       </c>
@@ -13348,8 +12576,8 @@
         <v>0.5</v>
       </c>
       <c r="J46" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K46:AAD46)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K46:AAB46)</f>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>149</v>
@@ -13369,14 +12597,8 @@
       <c r="T46" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U46" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V46" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>143</v>
       </c>
@@ -13405,7 +12627,7 @@
         <v>0.1111</v>
       </c>
       <c r="J47" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K47:AAD47)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K47:AAB47)</f>
         <v>missing_age_1</v>
       </c>
       <c r="K47" s="4"/>
@@ -13418,7 +12640,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>174</v>
       </c>
@@ -13447,8 +12669,8 @@
         <v>1</v>
       </c>
       <c r="J48" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K48:AAD48)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K48:AAB48)</f>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K48" s="9" t="s">
         <v>149</v>
@@ -13468,14 +12690,8 @@
       <c r="T48" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U48" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V48" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>174</v>
       </c>
@@ -13504,20 +12720,14 @@
         <v>0.125</v>
       </c>
       <c r="J49" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K49:AAD49)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K49:AAB49)</f>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U49" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V49" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>174</v>
       </c>
@@ -13546,14 +12756,14 @@
         <v>0.2</v>
       </c>
       <c r="J50" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K50:AAD50)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K50:AAB50)</f>
         <v>10-50+.all</v>
       </c>
       <c r="T50" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>174</v>
       </c>
@@ -13582,8 +12792,8 @@
         <v>0.5</v>
       </c>
       <c r="J51" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K51:AAD51)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K51:AAB51)</f>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>149</v>
@@ -13603,14 +12813,8 @@
       <c r="T51" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U51" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V51" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>143</v>
       </c>
@@ -13639,7 +12843,7 @@
         <v>0.1111</v>
       </c>
       <c r="J52" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K52:AAD52)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K52:AAB52)</f>
         <v>missing_age_1</v>
       </c>
       <c r="K52" s="4"/>
@@ -13652,7 +12856,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>174</v>
       </c>
@@ -13681,20 +12885,14 @@
         <v>0.125</v>
       </c>
       <c r="J53" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K53:AAD53)</f>
-        <v>&lt;15/&gt;15.d;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K53:AAB53)</f>
+        <v>&lt;15/&gt;15.d</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="U53" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V53" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>174</v>
       </c>
@@ -13723,8 +12921,8 @@
         <v>1</v>
       </c>
       <c r="J54" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K54:AAD54)</f>
-        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all;&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
+        <f>_xlfn.TEXTJOIN(";",1,K54:AAB54)</f>
+        <v>&lt;1-50+;1-50+;10-50+;15-50+;1-50+/&lt;5;10-50+.all</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>149</v>
@@ -13744,14 +12942,8 @@
       <c r="T54" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="U54" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V54" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>143</v>
       </c>
@@ -13780,7 +12972,7 @@
         <v>0.1111</v>
       </c>
       <c r="J55" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K55:AAD55)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K55:AAB55)</f>
         <v>missing_age_1</v>
       </c>
       <c r="K55" s="4"/>
@@ -13793,7 +12985,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>175</v>
       </c>
@@ -13822,20 +13014,20 @@
         <v>1</v>
       </c>
       <c r="J56" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K56:AAD56)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K56:AAB56)</f>
         <v>F;F/M;F/M/U</v>
       </c>
+      <c r="U56" t="s">
+        <v>141</v>
+      </c>
+      <c r="V56" t="s">
+        <v>145</v>
+      </c>
       <c r="W56" t="s">
-        <v>141</v>
-      </c>
-      <c r="X56" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y56" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>143</v>
       </c>
@@ -13864,7 +13056,7 @@
         <v>0.5</v>
       </c>
       <c r="J57" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K57:AAD57)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K57:AAB57)</f>
         <v>missing_sex_1</v>
       </c>
       <c r="K57" s="4"/>
@@ -13877,7 +13069,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>175</v>
       </c>
@@ -13906,7 +13098,7 @@
         <v>0.5</v>
       </c>
       <c r="J58" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K58:AAD58)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K58:AAB58)</f>
         <v>U;F/M/U</v>
       </c>
       <c r="K58" s="5"/>
@@ -13915,14 +13107,14 @@
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
+      <c r="U58" t="s">
+        <v>154</v>
+      </c>
       <c r="W58" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y58" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>175</v>
       </c>
@@ -13951,24 +13143,22 @@
         <v>1</v>
       </c>
       <c r="J59" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K59:AAD59)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K59:AAB59)</f>
         <v>M;F/M;F/M/U</v>
       </c>
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
-      <c r="U59" s="5"/>
-      <c r="V59" s="5"/>
+      <c r="U59" t="s">
+        <v>148</v>
+      </c>
+      <c r="V59" t="s">
+        <v>145</v>
+      </c>
       <c r="W59" t="s">
-        <v>148</v>
-      </c>
-      <c r="X59" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y59" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>143</v>
       </c>
@@ -13997,7 +13187,7 @@
         <v>0.5</v>
       </c>
       <c r="J60" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K60:AAD60)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K60:AAB60)</f>
         <v>missing_sex_1</v>
       </c>
       <c r="K60" s="4"/>
@@ -14010,7 +13200,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>175</v>
       </c>
@@ -14039,21 +13229,19 @@
         <v>0.5</v>
       </c>
       <c r="J61" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K61:AAD61)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K61:AAB61)</f>
         <v>U;F/M/U</v>
       </c>
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
-      <c r="U61" s="5"/>
-      <c r="V61" s="5"/>
+      <c r="U61" t="s">
+        <v>154</v>
+      </c>
       <c r="W61" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y61" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>184</v>
       </c>
@@ -14082,14 +13270,14 @@
         <v>1</v>
       </c>
       <c r="J62" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K62:AAD62)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K62:AAB62)</f>
         <v>kp1</v>
       </c>
-      <c r="Z62" t="s">
+      <c r="X62" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>184</v>
       </c>
@@ -14118,14 +13306,14 @@
         <v>1</v>
       </c>
       <c r="J63" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K63:AAD63)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K63:AAB63)</f>
         <v>kp1</v>
       </c>
-      <c r="Z63" t="s">
+      <c r="X63" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>184</v>
       </c>
@@ -14154,14 +13342,14 @@
         <v>1</v>
       </c>
       <c r="J64" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K64:AAD64)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K64:AAB64)</f>
         <v>kp1</v>
       </c>
-      <c r="Z64" t="s">
+      <c r="X64" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>184</v>
       </c>
@@ -14190,14 +13378,14 @@
         <v>1</v>
       </c>
       <c r="J65" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K65:AAD65)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K65:AAB65)</f>
         <v>kp1</v>
       </c>
-      <c r="Z65" t="s">
+      <c r="X65" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -14226,14 +13414,14 @@
         <v>1</v>
       </c>
       <c r="J66" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K66:AAD66)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K66:AAB66)</f>
         <v>kp1</v>
       </c>
-      <c r="Z66" t="s">
+      <c r="X66" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>196</v>
       </c>
@@ -14262,14 +13450,14 @@
         <v>1</v>
       </c>
       <c r="J67" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K67:AAD67)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K67:AAB67)</f>
         <v>tr_pos</v>
       </c>
-      <c r="AA67" t="s">
+      <c r="Y67" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>196</v>
       </c>
@@ -14298,14 +13486,14 @@
         <v>1</v>
       </c>
       <c r="J68" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K68:AAD68)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K68:AAB68)</f>
         <v>tr_neg</v>
       </c>
-      <c r="AA68" t="s">
+      <c r="Y68" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>264</v>
       </c>
@@ -14334,14 +13522,14 @@
         <v>1</v>
       </c>
       <c r="J69" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K69:AAD69)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K69:AAB69)</f>
         <v>tss_NewPos</v>
       </c>
-      <c r="AD69" t="s">
+      <c r="AB69" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>264</v>
       </c>
@@ -14370,14 +13558,14 @@
         <v>1</v>
       </c>
       <c r="J70" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K70:AAD70)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K70:AAB70)</f>
         <v>tss_KnowPos</v>
       </c>
-      <c r="AD70" t="s">
+      <c r="AB70" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>264</v>
       </c>
@@ -14406,14 +13594,14 @@
         <v>1</v>
       </c>
       <c r="J71" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K71:AAD71)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K71:AAB71)</f>
         <v>tss_NewNeg</v>
       </c>
-      <c r="AD71" t="s">
+      <c r="AB71" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>264</v>
       </c>
@@ -14421,13 +13609,13 @@
         <v>265</v>
       </c>
       <c r="C72" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="D72" t="s">
         <v>288</v>
       </c>
       <c r="E72" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="F72" t="s">
         <v>199</v>
@@ -14442,14 +13630,14 @@
         <v>1</v>
       </c>
       <c r="J72" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K72:AAD72)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K72:AAB72)</f>
         <v>tss_Pos</v>
       </c>
-      <c r="AD72" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AB72" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>264</v>
       </c>
@@ -14457,13 +13645,13 @@
         <v>265</v>
       </c>
       <c r="C73" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="D73" t="s">
         <v>288</v>
       </c>
       <c r="E73" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="F73" t="s">
         <v>201</v>
@@ -14478,14 +13666,14 @@
         <v>1</v>
       </c>
       <c r="J73" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K73:AAD73)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K73:AAB73)</f>
         <v>tss_Neg</v>
       </c>
-      <c r="AD73" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AB73" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>264</v>
       </c>
@@ -14493,19 +13681,19 @@
         <v>265</v>
       </c>
       <c r="C74" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="D74" t="s">
         <v>288</v>
       </c>
       <c r="E74" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="F74" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="G74" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="H74">
         <v>60</v>
@@ -14514,14 +13702,14 @@
         <v>1</v>
       </c>
       <c r="J74" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K74:AAD74)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K74:AAB74)</f>
         <v>tss_Unknown</v>
       </c>
-      <c r="AD74" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AB74" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>278</v>
       </c>
@@ -14550,14 +13738,14 @@
         <v>1</v>
       </c>
       <c r="J75" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K75:AAD75)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K75:AAB75)</f>
         <v>vt_sv</v>
       </c>
-      <c r="AE75" t="s">
+      <c r="AC75" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>278</v>
       </c>
@@ -14586,14 +13774,14 @@
         <v>1</v>
       </c>
       <c r="J76" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K76:AAD76)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K76:AAB76)</f>
         <v>vt_pe</v>
       </c>
-      <c r="AE76" t="s">
+      <c r="AC76" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>278</v>
       </c>
@@ -14622,14 +13810,14 @@
         <v>1</v>
       </c>
       <c r="J77" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K77:AAD77)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K77:AAB77)</f>
         <v>st_da</v>
       </c>
-      <c r="AF77" t="s">
+      <c r="AD77" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>278</v>
       </c>
@@ -14658,14 +13846,14 @@
         <v>1</v>
       </c>
       <c r="J78" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K78:AAD78)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K78:AAB78)</f>
         <v>st_da</v>
       </c>
-      <c r="AF78" t="s">
+      <c r="AD78" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>278</v>
       </c>
@@ -14694,14 +13882,14 @@
         <v>1</v>
       </c>
       <c r="J79" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K79:AAD79)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K79:AAB79)</f>
         <v>st_da</v>
       </c>
-      <c r="AF79" t="s">
+      <c r="AD79" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>278</v>
       </c>
@@ -14730,14 +13918,14 @@
         <v>1</v>
       </c>
       <c r="J80" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K80:AAD80)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K80:AAB80)</f>
         <v>st_da</v>
       </c>
-      <c r="AF80" t="s">
+      <c r="AD80" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>278</v>
       </c>
@@ -14766,14 +13954,14 @@
         <v>1</v>
       </c>
       <c r="J81" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K81:AAD81)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K81:AAB81)</f>
         <v>st_da</v>
       </c>
-      <c r="AF81" t="s">
+      <c r="AD81" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>278</v>
       </c>
@@ -14802,14 +13990,14 @@
         <v>1</v>
       </c>
       <c r="J82" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K82:AAD82)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K82:AAB82)</f>
         <v>st_da</v>
       </c>
-      <c r="AF82" t="s">
+      <c r="AD82" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>278</v>
       </c>
@@ -14838,14 +14026,14 @@
         <v>1</v>
       </c>
       <c r="J83" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K83:AAD83)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K83:AAB83)</f>
         <v>st_da</v>
       </c>
-      <c r="AF83" t="s">
+      <c r="AD83" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>278</v>
       </c>
@@ -14874,14 +14062,14 @@
         <v>1</v>
       </c>
       <c r="J84" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K84:AAD84)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K84:AAB84)</f>
         <v>st_da</v>
       </c>
-      <c r="AF84" t="s">
+      <c r="AD84" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>278</v>
       </c>
@@ -14910,14 +14098,14 @@
         <v>1</v>
       </c>
       <c r="J85" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K85:AAD85)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K85:AAB85)</f>
         <v>st_da</v>
       </c>
-      <c r="AF85" t="s">
+      <c r="AD85" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>278</v>
       </c>
@@ -14946,14 +14134,14 @@
         <v>1</v>
       </c>
       <c r="J86" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K86:AAD86)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K86:AAB86)</f>
         <v>st_da</v>
       </c>
-      <c r="AF86" t="s">
+      <c r="AD86" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>278</v>
       </c>
@@ -14982,14 +14170,14 @@
         <v>1</v>
       </c>
       <c r="J87" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K87:AAD87)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K87:AAB87)</f>
         <v>st_da</v>
       </c>
-      <c r="AF87" t="s">
+      <c r="AD87" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>278</v>
       </c>
@@ -15018,14 +14206,14 @@
         <v>1</v>
       </c>
       <c r="J88" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K88:AAD88)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K88:AAB88)</f>
         <v>st_da</v>
       </c>
-      <c r="AF88" t="s">
+      <c r="AD88" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>278</v>
       </c>
@@ -15054,14 +14242,14 @@
         <v>1</v>
       </c>
       <c r="J89" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K89:AAD89)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K89:AAB89)</f>
         <v>st_da</v>
       </c>
-      <c r="AF89" t="s">
+      <c r="AD89" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>278</v>
       </c>
@@ -15090,14 +14278,14 @@
         <v>1</v>
       </c>
       <c r="J90" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K90:AAD90)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K90:AAB90)</f>
         <v>st_da</v>
       </c>
-      <c r="AF90" t="s">
+      <c r="AD90" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>278</v>
       </c>
@@ -15126,14 +14314,14 @@
         <v>1</v>
       </c>
       <c r="J91" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K91:AAD91)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K91:AAB91)</f>
         <v>st_da</v>
       </c>
-      <c r="AF91" t="s">
+      <c r="AD91" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>278</v>
       </c>
@@ -15162,14 +14350,14 @@
         <v>1</v>
       </c>
       <c r="J92" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K92:AAD92)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K92:AAB92)</f>
         <v>st_da</v>
       </c>
-      <c r="AF92" t="s">
+      <c r="AD92" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>278</v>
       </c>
@@ -15198,14 +14386,14 @@
         <v>1</v>
       </c>
       <c r="J93" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K93:AAD93)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K93:AAB93)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF93" t="s">
+      <c r="AD93" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>278</v>
       </c>
@@ -15234,14 +14422,14 @@
         <v>1</v>
       </c>
       <c r="J94" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K94:AAD94)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K94:AAB94)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF94" t="s">
+      <c r="AD94" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>278</v>
       </c>
@@ -15270,14 +14458,14 @@
         <v>1</v>
       </c>
       <c r="J95" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K95:AAD95)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K95:AAB95)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF95" t="s">
+      <c r="AD95" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>278</v>
       </c>
@@ -15306,14 +14494,14 @@
         <v>1</v>
       </c>
       <c r="J96" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K96:AAD96)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K96:AAB96)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF96" t="s">
+      <c r="AD96" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>278</v>
       </c>
@@ -15342,14 +14530,14 @@
         <v>1</v>
       </c>
       <c r="J97" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K97:AAD97)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K97:AAB97)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF97" t="s">
+      <c r="AD97" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>278</v>
       </c>
@@ -15378,14 +14566,14 @@
         <v>1</v>
       </c>
       <c r="J98" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K98:AAD98)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K98:AAB98)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF98" t="s">
+      <c r="AD98" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>278</v>
       </c>
@@ -15414,14 +14602,14 @@
         <v>1</v>
       </c>
       <c r="J99" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K99:AAD99)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K99:AAB99)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF99" t="s">
+      <c r="AD99" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>278</v>
       </c>
@@ -15450,14 +14638,14 @@
         <v>1</v>
       </c>
       <c r="J100" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K100:AAD100)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K100:AAB100)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF100" t="s">
+      <c r="AD100" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>278</v>
       </c>
@@ -15486,14 +14674,14 @@
         <v>1</v>
       </c>
       <c r="J101" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K101:AAD101)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K101:AAB101)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF101" t="s">
+      <c r="AD101" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>278</v>
       </c>
@@ -15522,14 +14710,14 @@
         <v>1</v>
       </c>
       <c r="J102" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K102:AAD102)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K102:AAB102)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF102" t="s">
+      <c r="AD102" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="103" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>278</v>
       </c>
@@ -15558,14 +14746,14 @@
         <v>1</v>
       </c>
       <c r="J103" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K103:AAD103)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K103:AAB103)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF103" t="s">
+      <c r="AD103" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="104" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>278</v>
       </c>
@@ -15594,14 +14782,14 @@
         <v>1</v>
       </c>
       <c r="J104" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K104:AAD104)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K104:AAB104)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF104" t="s">
+      <c r="AD104" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="105" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>278</v>
       </c>
@@ -15630,14 +14818,14 @@
         <v>1</v>
       </c>
       <c r="J105" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K105:AAD105)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K105:AAB105)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF105" t="s">
+      <c r="AD105" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>278</v>
       </c>
@@ -15666,14 +14854,14 @@
         <v>1</v>
       </c>
       <c r="J106" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K106:AAD106)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K106:AAB106)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF106" t="s">
+      <c r="AD106" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>278</v>
       </c>
@@ -15702,14 +14890,14 @@
         <v>1</v>
       </c>
       <c r="J107" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K107:AAD107)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K107:AAB107)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF107" t="s">
+      <c r="AD107" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>278</v>
       </c>
@@ -15738,14 +14926,14 @@
         <v>1</v>
       </c>
       <c r="J108" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K108:AAD108)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K108:AAB108)</f>
         <v>st_ua</v>
       </c>
-      <c r="AF108" t="s">
+      <c r="AD108" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>278</v>
       </c>
@@ -15774,14 +14962,14 @@
         <v>1</v>
       </c>
       <c r="J109" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K109:AAD109)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K109:AAB109)</f>
         <v>kp2</v>
       </c>
-      <c r="Z109" t="s">
+      <c r="X109" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>278</v>
       </c>
@@ -15810,14 +14998,14 @@
         <v>1</v>
       </c>
       <c r="J110" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K110:AAD110)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K110:AAB110)</f>
         <v>kp2</v>
       </c>
-      <c r="Z110" t="s">
+      <c r="X110" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>278</v>
       </c>
@@ -15846,14 +15034,14 @@
         <v>1</v>
       </c>
       <c r="J111" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K111:AAD111)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K111:AAB111)</f>
         <v>kp2</v>
       </c>
-      <c r="Z111" t="s">
+      <c r="X111" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>278</v>
       </c>
@@ -15882,14 +15070,14 @@
         <v>1</v>
       </c>
       <c r="J112" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K112:AAD112)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K112:AAB112)</f>
         <v>kp2</v>
       </c>
-      <c r="Z112" t="s">
+      <c r="X112" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>278</v>
       </c>
@@ -15918,14 +15106,14 @@
         <v>1</v>
       </c>
       <c r="J113" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K113:AAD113)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K113:AAB113)</f>
         <v>kp2</v>
       </c>
-      <c r="Z113" t="s">
+      <c r="X113" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>278</v>
       </c>
@@ -15954,14 +15142,14 @@
         <v>1</v>
       </c>
       <c r="J114" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K114:AAD114)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K114:AAB114)</f>
         <v>kp2</v>
       </c>
-      <c r="Z114" t="s">
+      <c r="X114" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>278</v>
       </c>
@@ -15990,14 +15178,14 @@
         <v>1</v>
       </c>
       <c r="J115" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K115:AAD115)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K115:AAB115)</f>
         <v>kp2</v>
       </c>
-      <c r="Z115" t="s">
+      <c r="X115" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>278</v>
       </c>
@@ -16026,14 +15214,14 @@
         <v>1</v>
       </c>
       <c r="J116" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K116:AAD116)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K116:AAB116)</f>
         <v>kp2</v>
       </c>
-      <c r="Z116" t="s">
+      <c r="X116" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="117" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>381</v>
       </c>
@@ -16062,14 +15250,14 @@
         <v>1</v>
       </c>
       <c r="J117" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K117:AAD117)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K117:AAB117)</f>
         <v>as_already</v>
       </c>
-      <c r="AG117" t="s">
+      <c r="AE117" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="118" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>381</v>
       </c>
@@ -16098,14 +15286,14 @@
         <v>1</v>
       </c>
       <c r="J118" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K118:AAD118)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K118:AAB118)</f>
         <v>as_new</v>
       </c>
-      <c r="AG118" t="s">
+      <c r="AE118" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="119" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>278</v>
       </c>
@@ -16134,14 +15322,14 @@
         <v>1</v>
       </c>
       <c r="J119" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K119:AAD119)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K119:AAB119)</f>
         <v>kp3</v>
       </c>
-      <c r="Z119" t="s">
+      <c r="X119" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>278</v>
       </c>
@@ -16170,14 +15358,14 @@
         <v>1</v>
       </c>
       <c r="J120" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K120:AAD120)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K120:AAB120)</f>
         <v>kp3</v>
       </c>
-      <c r="Z120" t="s">
+      <c r="X120" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>278</v>
       </c>
@@ -16206,14 +15394,14 @@
         <v>1</v>
       </c>
       <c r="J121" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K121:AAD121)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K121:AAB121)</f>
         <v>kp3</v>
       </c>
-      <c r="Z121" t="s">
+      <c r="X121" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>278</v>
       </c>
@@ -16242,14 +15430,14 @@
         <v>1</v>
       </c>
       <c r="J122" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K122:AAD122)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K122:AAB122)</f>
         <v>kp3</v>
       </c>
-      <c r="Z122" t="s">
+      <c r="X122" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>278</v>
       </c>
@@ -16278,14 +15466,14 @@
         <v>1</v>
       </c>
       <c r="J123" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K123:AAD123)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K123:AAB123)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH123" t="s">
+      <c r="AF123" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>278</v>
       </c>
@@ -16314,14 +15502,14 @@
         <v>1</v>
       </c>
       <c r="J124" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K124:AAD124)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K124:AAB124)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH124" t="s">
+      <c r="AF124" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>278</v>
       </c>
@@ -16350,14 +15538,14 @@
         <v>1</v>
       </c>
       <c r="J125" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K125:AAD125)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K125:AAB125)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH125" t="s">
+      <c r="AF125" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>278</v>
       </c>
@@ -16386,14 +15574,14 @@
         <v>1</v>
       </c>
       <c r="J126" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K126:AAD126)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K126:AAB126)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH126" t="s">
+      <c r="AF126" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="127" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>278</v>
       </c>
@@ -16401,13 +15589,13 @@
         <v>416</v>
       </c>
       <c r="C127" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="D127" t="s">
         <v>402</v>
       </c>
       <c r="E127" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="F127" t="s">
         <v>412</v>
@@ -16422,14 +15610,14 @@
         <v>1</v>
       </c>
       <c r="J127" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K127:AAD127)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K127:AAB127)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH127" t="s">
+      <c r="AF127" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="128" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>278</v>
       </c>
@@ -16437,13 +15625,13 @@
         <v>416</v>
       </c>
       <c r="C128" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D128" t="s">
         <v>402</v>
       </c>
       <c r="E128" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="F128" t="s">
         <v>412</v>
@@ -16458,14 +15646,14 @@
         <v>1</v>
       </c>
       <c r="J128" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K128:AAD128)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K128:AAB128)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH128" t="s">
+      <c r="AF128" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="129" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>278</v>
       </c>
@@ -16473,13 +15661,13 @@
         <v>416</v>
       </c>
       <c r="C129" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="D129" t="s">
         <v>402</v>
       </c>
       <c r="E129" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="F129" t="s">
         <v>412</v>
@@ -16494,14 +15682,14 @@
         <v>1</v>
       </c>
       <c r="J129" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K129:AAD129)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K129:AAB129)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH129" t="s">
+      <c r="AF129" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="130" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>278</v>
       </c>
@@ -16509,13 +15697,13 @@
         <v>416</v>
       </c>
       <c r="C130" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="D130" t="s">
         <v>402</v>
       </c>
       <c r="E130" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="F130" t="s">
         <v>412</v>
@@ -16530,14 +15718,14 @@
         <v>1</v>
       </c>
       <c r="J130" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K130:AAD130)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K130:AAB130)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH130" t="s">
+      <c r="AF130" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="131" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>278</v>
       </c>
@@ -16545,13 +15733,13 @@
         <v>416</v>
       </c>
       <c r="C131" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="D131" t="s">
         <v>402</v>
       </c>
       <c r="E131" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="F131" t="s">
         <v>412</v>
@@ -16566,14 +15754,14 @@
         <v>1</v>
       </c>
       <c r="J131" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K131:AAD131)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K131:AAB131)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH131" t="s">
+      <c r="AF131" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="132" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>278</v>
       </c>
@@ -16581,13 +15769,13 @@
         <v>416</v>
       </c>
       <c r="C132" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="D132" t="s">
         <v>402</v>
       </c>
       <c r="E132" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="F132" t="s">
         <v>412</v>
@@ -16602,14 +15790,14 @@
         <v>1</v>
       </c>
       <c r="J132" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K132:AAD132)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K132:AAB132)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH132" t="s">
+      <c r="AF132" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="133" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>278</v>
       </c>
@@ -16617,13 +15805,13 @@
         <v>416</v>
       </c>
       <c r="C133" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="D133" t="s">
         <v>402</v>
       </c>
       <c r="E133" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="F133" t="s">
         <v>412</v>
@@ -16638,14 +15826,14 @@
         <v>1</v>
       </c>
       <c r="J133" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K133:AAD133)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K133:AAB133)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH133" t="s">
+      <c r="AF133" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="134" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>278</v>
       </c>
@@ -16653,13 +15841,13 @@
         <v>416</v>
       </c>
       <c r="C134" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="D134" t="s">
         <v>402</v>
       </c>
       <c r="E134" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="F134" t="s">
         <v>412</v>
@@ -16674,14 +15862,14 @@
         <v>1</v>
       </c>
       <c r="J134" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K134:AAD134)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K134:AAB134)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH134" t="s">
+      <c r="AF134" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="135" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>278</v>
       </c>
@@ -16689,13 +15877,13 @@
         <v>416</v>
       </c>
       <c r="C135" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="D135" t="s">
         <v>402</v>
       </c>
       <c r="E135" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="F135" t="s">
         <v>412</v>
@@ -16710,14 +15898,14 @@
         <v>1</v>
       </c>
       <c r="J135" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K135:AAD135)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K135:AAB135)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH135" t="s">
+      <c r="AF135" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="136" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>278</v>
       </c>
@@ -16725,13 +15913,13 @@
         <v>416</v>
       </c>
       <c r="C136" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="D136" t="s">
         <v>402</v>
       </c>
       <c r="E136" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="F136" t="s">
         <v>412</v>
@@ -16746,14 +15934,14 @@
         <v>1</v>
       </c>
       <c r="J136" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K136:AAD136)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K136:AAB136)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH136" t="s">
+      <c r="AF136" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="137" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>278</v>
       </c>
@@ -16761,13 +15949,13 @@
         <v>416</v>
       </c>
       <c r="C137" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="D137" t="s">
         <v>402</v>
       </c>
       <c r="E137" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="F137" t="s">
         <v>412</v>
@@ -16782,14 +15970,14 @@
         <v>1</v>
       </c>
       <c r="J137" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K137:AAD137)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K137:AAB137)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH137" t="s">
+      <c r="AF137" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="138" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>278</v>
       </c>
@@ -16797,13 +15985,13 @@
         <v>416</v>
       </c>
       <c r="C138" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="D138" t="s">
         <v>402</v>
       </c>
       <c r="E138" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="F138" t="s">
         <v>412</v>
@@ -16818,14 +16006,14 @@
         <v>1</v>
       </c>
       <c r="J138" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K138:AAD138)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K138:AAB138)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH138" t="s">
+      <c r="AF138" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="139" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>278</v>
       </c>
@@ -16833,13 +16021,13 @@
         <v>416</v>
       </c>
       <c r="C139" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="D139" t="s">
         <v>402</v>
       </c>
       <c r="E139" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="F139" t="s">
         <v>412</v>
@@ -16854,14 +16042,14 @@
         <v>1</v>
       </c>
       <c r="J139" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K139:AAD139)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K139:AAB139)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH139" t="s">
+      <c r="AF139" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="140" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>278</v>
       </c>
@@ -16869,13 +16057,13 @@
         <v>416</v>
       </c>
       <c r="C140" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="D140" t="s">
         <v>402</v>
       </c>
       <c r="E140" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="F140" t="s">
         <v>412</v>
@@ -16890,14 +16078,14 @@
         <v>1</v>
       </c>
       <c r="J140" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K140:AAD140)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K140:AAB140)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH140" t="s">
+      <c r="AF140" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="141" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>278</v>
       </c>
@@ -16905,13 +16093,13 @@
         <v>416</v>
       </c>
       <c r="C141" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="D141" t="s">
         <v>402</v>
       </c>
       <c r="E141" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="F141" t="s">
         <v>412</v>
@@ -16926,14 +16114,14 @@
         <v>1</v>
       </c>
       <c r="J141" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K141:AAD141)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K141:AAB141)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH141" t="s">
+      <c r="AF141" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="142" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>278</v>
       </c>
@@ -16941,13 +16129,13 @@
         <v>416</v>
       </c>
       <c r="C142" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="D142" t="s">
         <v>402</v>
       </c>
       <c r="E142" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="F142" t="s">
         <v>412</v>
@@ -16962,14 +16150,14 @@
         <v>1</v>
       </c>
       <c r="J142" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K142:AAD142)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K142:AAB142)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH142" t="s">
+      <c r="AF142" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="143" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>278</v>
       </c>
@@ -16977,13 +16165,13 @@
         <v>416</v>
       </c>
       <c r="C143" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="D143" t="s">
         <v>402</v>
       </c>
       <c r="E143" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="F143" t="s">
         <v>412</v>
@@ -16998,14 +16186,14 @@
         <v>1</v>
       </c>
       <c r="J143" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K143:AAD143)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K143:AAB143)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH143" t="s">
+      <c r="AF143" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="144" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>278</v>
       </c>
@@ -17013,13 +16201,13 @@
         <v>416</v>
       </c>
       <c r="C144" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="D144" t="s">
         <v>402</v>
       </c>
       <c r="E144" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="F144" t="s">
         <v>412</v>
@@ -17034,14 +16222,14 @@
         <v>1</v>
       </c>
       <c r="J144" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K144:AAD144)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K144:AAB144)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH144" t="s">
+      <c r="AF144" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="145" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>278</v>
       </c>
@@ -17049,13 +16237,13 @@
         <v>416</v>
       </c>
       <c r="C145" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="D145" t="s">
         <v>402</v>
       </c>
       <c r="E145" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="F145" t="s">
         <v>412</v>
@@ -17070,14 +16258,14 @@
         <v>1</v>
       </c>
       <c r="J145" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K145:AAD145)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K145:AAB145)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH145" t="s">
+      <c r="AF145" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="146" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>278</v>
       </c>
@@ -17085,13 +16273,13 @@
         <v>416</v>
       </c>
       <c r="C146" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="D146" t="s">
         <v>402</v>
       </c>
       <c r="E146" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="F146" t="s">
         <v>412</v>
@@ -17106,14 +16294,14 @@
         <v>1</v>
       </c>
       <c r="J146" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K146:AAD146)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K146:AAB146)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH146" t="s">
+      <c r="AF146" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="147" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>278</v>
       </c>
@@ -17121,13 +16309,13 @@
         <v>416</v>
       </c>
       <c r="C147" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="D147" t="s">
         <v>402</v>
       </c>
       <c r="E147" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="F147" t="s">
         <v>412</v>
@@ -17142,14 +16330,14 @@
         <v>1</v>
       </c>
       <c r="J147" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K147:AAD147)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K147:AAB147)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH147" t="s">
+      <c r="AF147" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="148" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>278</v>
       </c>
@@ -17157,13 +16345,13 @@
         <v>416</v>
       </c>
       <c r="C148" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="D148" t="s">
         <v>402</v>
       </c>
       <c r="E148" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="F148" t="s">
         <v>412</v>
@@ -17178,14 +16366,14 @@
         <v>1</v>
       </c>
       <c r="J148" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K148:AAD148)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K148:AAB148)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH148" t="s">
+      <c r="AF148" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="149" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>278</v>
       </c>
@@ -17193,13 +16381,13 @@
         <v>416</v>
       </c>
       <c r="C149" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="D149" t="s">
         <v>402</v>
       </c>
       <c r="E149" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="F149" t="s">
         <v>412</v>
@@ -17214,14 +16402,14 @@
         <v>1</v>
       </c>
       <c r="J149" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K149:AAD149)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K149:AAB149)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH149" t="s">
+      <c r="AF149" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="150" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>278</v>
       </c>
@@ -17229,13 +16417,13 @@
         <v>416</v>
       </c>
       <c r="C150" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="D150" t="s">
         <v>402</v>
       </c>
       <c r="E150" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="F150" t="s">
         <v>412</v>
@@ -17250,14 +16438,14 @@
         <v>1</v>
       </c>
       <c r="J150" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K150:AAD150)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K150:AAB150)</f>
         <v>ti_routine</v>
       </c>
-      <c r="AH150" t="s">
+      <c r="AF150" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="151" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>196</v>
       </c>
@@ -17286,14 +16474,14 @@
         <v>1</v>
       </c>
       <c r="J151" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K151:AAD151)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K151:AAB151)</f>
         <v>tr_pos2</v>
       </c>
-      <c r="AA151" t="s">
+      <c r="Y151" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="152" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>196</v>
       </c>
@@ -17322,14 +16510,14 @@
         <v>1</v>
       </c>
       <c r="J152" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K152:AAD152)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K152:AAB152)</f>
         <v>tr_neg2</v>
       </c>
-      <c r="AA152" t="s">
+      <c r="Y152" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="153" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>509</v>
       </c>
@@ -17358,14 +16546,14 @@
         <v>1</v>
       </c>
       <c r="J153" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K153:AAD153)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K153:AAB153)</f>
         <v>hts_mod_com_ndx</v>
       </c>
-      <c r="AK153" t="s">
+      <c r="AI153" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="154" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>509</v>
       </c>
@@ -17394,14 +16582,14 @@
         <v>1</v>
       </c>
       <c r="J154" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K154:AAD154)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K154:AAB154)</f>
         <v>hts_mod_fac_ndx</v>
       </c>
-      <c r="AK154" t="s">
+      <c r="AI154" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="155" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>509</v>
       </c>
@@ -17430,14 +16618,14 @@
         <v>1</v>
       </c>
       <c r="J155" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K155:AAD155)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K155:AAB155)</f>
         <v>hts_mod_com_mob</v>
       </c>
-      <c r="AK155" t="s">
+      <c r="AI155" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="156" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>509</v>
       </c>
@@ -17466,14 +16654,14 @@
         <v>1</v>
       </c>
       <c r="J156" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K156:AAD156)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K156:AAB156)</f>
         <v>hts_mod_com_vct</v>
       </c>
-      <c r="AK156" t="s">
+      <c r="AI156" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="157" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>509</v>
       </c>
@@ -17502,14 +16690,14 @@
         <v>1</v>
       </c>
       <c r="J157" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K157:AAD157)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K157:AAB157)</f>
         <v>hts_mod_com_otr</v>
       </c>
-      <c r="AK157" t="s">
+      <c r="AI157" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="158" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>509</v>
       </c>
@@ -17538,14 +16726,14 @@
         <v>1</v>
       </c>
       <c r="J158" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K158:AAD158)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K158:AAB158)</f>
         <v>hts_mod_fac_ew</v>
       </c>
-      <c r="AK158" t="s">
+      <c r="AI158" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="159" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>509</v>
       </c>
@@ -17574,14 +16762,14 @@
         <v>1</v>
       </c>
       <c r="J159" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K159:AAD159)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K159:AAB159)</f>
         <v>hts_mod_fac_inpat</v>
       </c>
-      <c r="AK159" t="s">
+      <c r="AI159" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="160" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>509</v>
       </c>
@@ -17610,14 +16798,14 @@
         <v>1</v>
       </c>
       <c r="J160" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K160:AAD160)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K160:AAB160)</f>
         <v>hts_mod_fac_nut</v>
       </c>
-      <c r="AK160" t="s">
+      <c r="AI160" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="161" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>509</v>
       </c>
@@ -17646,14 +16834,14 @@
         <v>1</v>
       </c>
       <c r="J161" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K161:AAD161)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K161:AAB161)</f>
         <v>hts_mod_fac_ped</v>
       </c>
-      <c r="AK161" t="s">
+      <c r="AI161" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="162" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>509</v>
       </c>
@@ -17682,14 +16870,14 @@
         <v>1</v>
       </c>
       <c r="J162" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K162:AAD162)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K162:AAB162)</f>
         <v>hts_mod_fac_sti</v>
       </c>
-      <c r="AK162" t="s">
+      <c r="AI162" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="163" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>509</v>
       </c>
@@ -17718,14 +16906,14 @@
         <v>1</v>
       </c>
       <c r="J163" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K163:AAD163)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K163:AAB163)</f>
         <v>hts_mod_fac_vct</v>
       </c>
-      <c r="AK163" t="s">
+      <c r="AI163" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="164" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>509</v>
       </c>
@@ -17754,14 +16942,14 @@
         <v>1</v>
       </c>
       <c r="J164" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K164:AAD164)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K164:AAB164)</f>
         <v>hts_mod_fac_otr_pitc</v>
       </c>
-      <c r="AK164" t="s">
+      <c r="AI164" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="165" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>509</v>
       </c>
@@ -17790,14 +16978,14 @@
         <v>1</v>
       </c>
       <c r="J165" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K165:AAD165)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K165:AAB165)</f>
         <v>hts_mod_fac_vmmc</v>
       </c>
-      <c r="AK165" t="s">
+      <c r="AI165" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="166" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>509</v>
       </c>
@@ -17826,14 +17014,14 @@
         <v>1</v>
       </c>
       <c r="J166" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K166:AAD166)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K166:AAB166)</f>
         <v>hts_mod_fac_anc_1</v>
       </c>
-      <c r="AK166" t="s">
+      <c r="AI166" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="167" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>509</v>
       </c>
@@ -17862,14 +17050,14 @@
         <v>1</v>
       </c>
       <c r="J167" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K167:AAD167)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K167:AAB167)</f>
         <v>hts_mod_fac_tb</v>
       </c>
-      <c r="AK167" t="s">
+      <c r="AI167" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="168" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>509</v>
       </c>
@@ -17898,14 +17086,14 @@
         <v>1</v>
       </c>
       <c r="J168" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K168:AAD168)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K168:AAB168)</f>
         <v>hts_mod_fac_post_anc_1</v>
       </c>
-      <c r="AK168" t="s">
+      <c r="AI168" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="169" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>174</v>
       </c>
@@ -17934,7 +17122,7 @@
         <v>1</v>
       </c>
       <c r="J169" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K169:AAD169)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K169:AAB169)</f>
         <v>U_age</v>
       </c>
       <c r="K169" s="9"/>
@@ -17945,13 +17133,11 @@
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
       <c r="T169" s="9"/>
-      <c r="U169" s="9"/>
-      <c r="V169" s="9"/>
-      <c r="AK169" t="s">
+      <c r="AI169" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="170" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>175</v>
       </c>
@@ -17980,562 +17166,496 @@
         <v>1</v>
       </c>
       <c r="J170" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K170:AAD170)</f>
+        <f>_xlfn.TEXTJOIN(";",1,K170:AAB170)</f>
         <v>U_sex</v>
       </c>
-      <c r="AK170" t="s">
+      <c r="AI170" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="171" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>174</v>
+        <v>678</v>
       </c>
       <c r="B171" t="s">
-        <v>233</v>
+        <v>679</v>
       </c>
       <c r="C171" t="s">
-        <v>519</v>
+        <v>674</v>
       </c>
       <c r="D171" t="s">
-        <v>217</v>
+        <v>436</v>
       </c>
       <c r="E171" t="s">
-        <v>520</v>
+        <v>675</v>
       </c>
       <c r="F171" t="s">
-        <v>99</v>
+        <v>675</v>
       </c>
       <c r="G171" t="s">
-        <v>114</v>
+        <v>674</v>
       </c>
       <c r="H171" s="7">
-        <v>10</v>
-      </c>
-      <c r="I171" s="13">
-        <v>8.3299999999999999E-2</v>
+        <v>1</v>
+      </c>
+      <c r="I171" s="12">
+        <v>1</v>
       </c>
       <c r="J171" s="4" t="str">
-        <f t="shared" ref="J171:J184" si="0">_xlfn.TEXTJOIN(";",1,K171:AAD171)</f>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U171" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V171" s="19"/>
-    </row>
-    <row r="172" spans="1:37" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K171:AAB171)</f>
+        <v>ag_a</v>
+      </c>
+      <c r="AG171" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="172" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>174</v>
+        <v>678</v>
       </c>
       <c r="B172" t="s">
-        <v>233</v>
+        <v>679</v>
       </c>
       <c r="C172" t="s">
-        <v>519</v>
+        <v>676</v>
       </c>
       <c r="D172" t="s">
-        <v>217</v>
+        <v>436</v>
       </c>
       <c r="E172" t="s">
-        <v>520</v>
+        <v>677</v>
       </c>
       <c r="F172" t="s">
-        <v>97</v>
+        <v>677</v>
       </c>
       <c r="G172" t="s">
-        <v>117</v>
-      </c>
-      <c r="H172" s="6">
-        <v>15</v>
-      </c>
-      <c r="I172" s="13">
-        <v>8.3299999999999999E-2</v>
+        <v>676</v>
+      </c>
+      <c r="H172" s="7">
+        <v>2</v>
+      </c>
+      <c r="I172" s="12">
+        <v>1</v>
       </c>
       <c r="J172" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U172" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V172" s="9"/>
-    </row>
-    <row r="173" spans="1:37" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K172:AAB172)</f>
+        <v>ag_g</v>
+      </c>
+      <c r="AG172" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="173" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B173" t="s">
-        <v>233</v>
-      </c>
-      <c r="C173" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C173" s="21" t="s">
+        <v>766</v>
       </c>
       <c r="D173" t="s">
-        <v>217</v>
-      </c>
-      <c r="E173" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E173" s="21" t="s">
+        <v>765</v>
       </c>
       <c r="F173" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="G173" t="s">
-        <v>127</v>
-      </c>
-      <c r="H173" s="7">
-        <v>30</v>
-      </c>
-      <c r="I173" s="13">
-        <v>8.3299999999999999E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I173" s="12">
+        <v>1</v>
       </c>
       <c r="J173" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U173" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V173" s="9"/>
-    </row>
-    <row r="174" spans="1:37" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K173:AAB173)</f>
+        <v>tb_n_art_a</v>
+      </c>
+      <c r="AH173" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="174" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B174" t="s">
-        <v>233</v>
-      </c>
-      <c r="C174" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C174" s="21" t="s">
+        <v>768</v>
       </c>
       <c r="D174" t="s">
-        <v>217</v>
-      </c>
-      <c r="E174" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E174" s="21" t="s">
+        <v>767</v>
       </c>
       <c r="F174" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="G174" t="s">
-        <v>118</v>
-      </c>
-      <c r="H174" s="7">
-        <v>40</v>
-      </c>
-      <c r="I174" s="13">
-        <v>8.3299999999999999E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I174" s="12">
+        <v>1</v>
       </c>
       <c r="J174" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(";",1,K174:AAD174)</f>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U174" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V174" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="175" spans="1:37" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K174:AAB174)</f>
+        <v>tb_n_art_a</v>
+      </c>
+      <c r="AH174" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="175" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B175" t="s">
-        <v>233</v>
-      </c>
-      <c r="C175" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C175" s="21" t="s">
+        <v>770</v>
       </c>
       <c r="D175" t="s">
-        <v>217</v>
-      </c>
-      <c r="E175" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E175" s="21" t="s">
+        <v>769</v>
       </c>
       <c r="F175" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="G175" t="s">
-        <v>120</v>
-      </c>
-      <c r="H175" s="7">
-        <v>60</v>
-      </c>
-      <c r="I175" s="13">
-        <v>8.3400000000000002E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I175" s="12">
+        <v>1</v>
       </c>
       <c r="J175" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U175" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V175" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="176" spans="1:37" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K175:AAB175)</f>
+        <v>tb_n_art_n</v>
+      </c>
+      <c r="AH175" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="176" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B176" t="s">
-        <v>233</v>
-      </c>
-      <c r="C176" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C176" s="21" t="s">
+        <v>772</v>
       </c>
       <c r="D176" t="s">
-        <v>217</v>
-      </c>
-      <c r="E176" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E176" s="21" t="s">
+        <v>771</v>
       </c>
       <c r="F176" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="G176" t="s">
-        <v>121</v>
-      </c>
-      <c r="H176" s="7">
-        <v>80</v>
-      </c>
-      <c r="I176" s="13">
-        <v>8.3400000000000002E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I176" s="12">
+        <v>1</v>
       </c>
       <c r="J176" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U176" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V176" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="177" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K176:AAB176)</f>
+        <v>tb_n_art_n</v>
+      </c>
+      <c r="AH176" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="177" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
-      </c>
-      <c r="C177" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C177" s="21" t="s">
+        <v>774</v>
       </c>
       <c r="D177" t="s">
-        <v>217</v>
-      </c>
-      <c r="E177" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E177" s="21" t="s">
+        <v>773</v>
       </c>
       <c r="F177" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="G177" t="s">
-        <v>122</v>
-      </c>
-      <c r="H177" s="7">
-        <v>90</v>
-      </c>
-      <c r="I177" s="13">
-        <v>8.3400000000000002E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I177" s="12">
+        <v>1</v>
       </c>
       <c r="J177" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U177" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V177" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="178" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K177:AAB177)</f>
+        <v>tb_p_art_a</v>
+      </c>
+      <c r="AH177" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="178" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B178" t="s">
-        <v>233</v>
-      </c>
-      <c r="C178" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C178" s="21" t="s">
+        <v>776</v>
       </c>
       <c r="D178" t="s">
-        <v>217</v>
-      </c>
-      <c r="E178" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E178" s="21" t="s">
+        <v>775</v>
       </c>
       <c r="F178" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="G178" t="s">
-        <v>123</v>
-      </c>
-      <c r="H178" s="7">
-        <v>110</v>
-      </c>
-      <c r="I178" s="13">
-        <v>8.3400000000000002E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I178" s="12">
+        <v>1</v>
       </c>
       <c r="J178" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U178" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V178" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="179" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K178:AAB178)</f>
+        <v>tb_p_art_a</v>
+      </c>
+      <c r="AH178" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="179" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B179" t="s">
-        <v>233</v>
-      </c>
-      <c r="C179" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C179" s="21" t="s">
+        <v>778</v>
       </c>
       <c r="D179" t="s">
-        <v>217</v>
-      </c>
-      <c r="E179" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E179" s="21" t="s">
+        <v>777</v>
       </c>
       <c r="F179" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="G179" t="s">
-        <v>124</v>
-      </c>
-      <c r="H179" s="7">
-        <v>120</v>
-      </c>
-      <c r="I179" s="13">
-        <v>8.3299999999999999E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I179" s="12">
+        <v>1</v>
       </c>
       <c r="J179" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U179" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V179" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="180" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K179:AAB179)</f>
+        <v>tb_p_art_n</v>
+      </c>
+      <c r="AH179" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="180" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B180" t="s">
-        <v>233</v>
-      </c>
-      <c r="C180" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C180" s="21" t="s">
+        <v>780</v>
       </c>
       <c r="D180" t="s">
-        <v>217</v>
-      </c>
-      <c r="E180" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E180" s="21" t="s">
+        <v>779</v>
       </c>
       <c r="F180" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="G180" t="s">
-        <v>125</v>
-      </c>
-      <c r="H180" s="7">
-        <v>130</v>
-      </c>
-      <c r="I180" s="13">
-        <v>8.3299999999999999E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I180" s="12">
+        <v>1</v>
       </c>
       <c r="J180" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U180" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V180" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="181" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K180:AAB180)</f>
+        <v>tb_p_art_n</v>
+      </c>
+      <c r="AH180" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="181" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B181" t="s">
-        <v>233</v>
-      </c>
-      <c r="C181" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C181" s="21" t="s">
+        <v>782</v>
       </c>
       <c r="D181" t="s">
-        <v>217</v>
-      </c>
-      <c r="E181" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E181" s="21" t="s">
+        <v>781</v>
       </c>
       <c r="F181" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="G181" t="s">
-        <v>126</v>
-      </c>
-      <c r="H181" s="7">
-        <v>140</v>
-      </c>
-      <c r="I181" s="13">
-        <v>8.3299999999999999E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I181" s="12">
+        <v>1</v>
       </c>
       <c r="J181" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U181" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V181" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="182" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K181:AAB181)</f>
+        <v>tb_n_art_a</v>
+      </c>
+      <c r="AH181" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="182" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B182" t="s">
-        <v>233</v>
-      </c>
-      <c r="C182" t="s">
-        <v>519</v>
+        <v>416</v>
+      </c>
+      <c r="C182" s="21" t="s">
+        <v>784</v>
       </c>
       <c r="D182" t="s">
-        <v>217</v>
-      </c>
-      <c r="E182" t="s">
-        <v>520</v>
+        <v>436</v>
+      </c>
+      <c r="E182" s="21" t="s">
+        <v>783</v>
       </c>
       <c r="F182" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="G182" t="s">
-        <v>116</v>
-      </c>
-      <c r="H182" s="7">
-        <v>150</v>
-      </c>
-      <c r="I182" s="13">
-        <v>8.3299999999999999E-2</v>
+        <v>143</v>
+      </c>
+      <c r="I182" s="12">
+        <v>1</v>
       </c>
       <c r="J182" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;1-50+.&lt;15/&gt;15.d.u;10-50+.&lt;15/&gt;15.d.u</v>
-      </c>
-      <c r="U182" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="V182" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="183" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K182:AAB182)</f>
+        <v>tb_n_art_a</v>
+      </c>
+      <c r="AH182" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="183" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>691</v>
+        <v>278</v>
       </c>
       <c r="B183" t="s">
-        <v>692</v>
-      </c>
-      <c r="C183" t="s">
-        <v>687</v>
+        <v>416</v>
+      </c>
+      <c r="C183" s="21" t="s">
+        <v>786</v>
       </c>
       <c r="D183" t="s">
         <v>436</v>
       </c>
-      <c r="E183" t="s">
-        <v>688</v>
+      <c r="E183" s="21" t="s">
+        <v>785</v>
       </c>
       <c r="F183" t="s">
-        <v>688</v>
+        <v>143</v>
       </c>
       <c r="G183" t="s">
-        <v>687</v>
-      </c>
-      <c r="H183" s="7">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="I183" s="12">
         <v>1</v>
       </c>
       <c r="J183" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>ag_a</v>
-      </c>
-      <c r="AI183" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="184" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K183:AAB183)</f>
+        <v>tb_n_art_n</v>
+      </c>
+      <c r="AH183" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="184" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>691</v>
+        <v>278</v>
       </c>
       <c r="B184" t="s">
-        <v>692</v>
-      </c>
-      <c r="C184" t="s">
-        <v>689</v>
+        <v>416</v>
+      </c>
+      <c r="C184" s="21" t="s">
+        <v>788</v>
       </c>
       <c r="D184" t="s">
         <v>436</v>
       </c>
-      <c r="E184" t="s">
-        <v>690</v>
+      <c r="E184" s="21" t="s">
+        <v>787</v>
       </c>
       <c r="F184" t="s">
-        <v>690</v>
+        <v>143</v>
       </c>
       <c r="G184" t="s">
-        <v>689</v>
-      </c>
-      <c r="H184" s="7">
-        <v>2</v>
+        <v>143</v>
       </c>
       <c r="I184" s="12">
         <v>1</v>
       </c>
       <c r="J184" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>ag_g</v>
-      </c>
-      <c r="AI184" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="185" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K184:AAB184)</f>
+        <v>tb_n_art_n</v>
+      </c>
+      <c r="AH184" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="185" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>278</v>
       </c>
       <c r="B185" t="s">
         <v>416</v>
       </c>
-      <c r="C185" s="22" t="s">
-        <v>779</v>
+      <c r="C185" s="21" t="s">
+        <v>790</v>
       </c>
       <c r="D185" t="s">
         <v>436</v>
       </c>
-      <c r="E185" s="22" t="s">
-        <v>778</v>
+      <c r="E185" s="21" t="s">
+        <v>789</v>
       </c>
       <c r="F185" t="s">
         <v>143</v>
@@ -18547,28 +17667,28 @@
         <v>1</v>
       </c>
       <c r="J185" s="4" t="str">
-        <f t="shared" ref="J185:J200" si="1">_xlfn.TEXTJOIN(";",1,K185:AAD185)</f>
-        <v>tb_n_art_a</v>
-      </c>
-      <c r="AJ185" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="186" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K185:AAB185)</f>
+        <v>tb_p_art_a</v>
+      </c>
+      <c r="AH185" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="186" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>278</v>
       </c>
       <c r="B186" t="s">
         <v>416</v>
       </c>
-      <c r="C186" s="22" t="s">
-        <v>781</v>
+      <c r="C186" s="21" t="s">
+        <v>792</v>
       </c>
       <c r="D186" t="s">
         <v>436</v>
       </c>
-      <c r="E186" s="22" t="s">
-        <v>780</v>
+      <c r="E186" s="21" t="s">
+        <v>791</v>
       </c>
       <c r="F186" t="s">
         <v>143</v>
@@ -18580,28 +17700,28 @@
         <v>1</v>
       </c>
       <c r="J186" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_n_art_a</v>
-      </c>
-      <c r="AJ186" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="187" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K186:AAB186)</f>
+        <v>tb_p_art_a</v>
+      </c>
+      <c r="AH186" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="187" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>278</v>
       </c>
       <c r="B187" t="s">
         <v>416</v>
       </c>
-      <c r="C187" s="22" t="s">
-        <v>783</v>
+      <c r="C187" s="21" t="s">
+        <v>794</v>
       </c>
       <c r="D187" t="s">
         <v>436</v>
       </c>
-      <c r="E187" s="22" t="s">
-        <v>782</v>
+      <c r="E187" s="21" t="s">
+        <v>793</v>
       </c>
       <c r="F187" t="s">
         <v>143</v>
@@ -18613,28 +17733,28 @@
         <v>1</v>
       </c>
       <c r="J187" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_n_art_n</v>
-      </c>
-      <c r="AJ187" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="188" spans="1:36" x14ac:dyDescent="0.2">
+        <f>_xlfn.TEXTJOIN(";",1,K187:AAB187)</f>
+        <v>tb_p_art_n</v>
+      </c>
+      <c r="AH187" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="188" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>278</v>
       </c>
       <c r="B188" t="s">
         <v>416</v>
       </c>
-      <c r="C188" s="22" t="s">
-        <v>785</v>
+      <c r="C188" s="21" t="s">
+        <v>796</v>
       </c>
       <c r="D188" t="s">
         <v>436</v>
       </c>
-      <c r="E188" s="22" t="s">
-        <v>784</v>
+      <c r="E188" s="21" t="s">
+        <v>795</v>
       </c>
       <c r="F188" t="s">
         <v>143</v>
@@ -18646,412 +17766,16 @@
         <v>1</v>
       </c>
       <c r="J188" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_n_art_n</v>
-      </c>
-      <c r="AJ188" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="189" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A189" t="s">
-        <v>278</v>
-      </c>
-      <c r="B189" t="s">
-        <v>416</v>
-      </c>
-      <c r="C189" s="22" t="s">
-        <v>787</v>
-      </c>
-      <c r="D189" t="s">
-        <v>436</v>
-      </c>
-      <c r="E189" s="22" t="s">
-        <v>786</v>
-      </c>
-      <c r="F189" t="s">
-        <v>143</v>
-      </c>
-      <c r="G189" t="s">
-        <v>143</v>
-      </c>
-      <c r="I189" s="12">
-        <v>1</v>
-      </c>
-      <c r="J189" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_p_art_a</v>
-      </c>
-      <c r="AJ189" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="190" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A190" t="s">
-        <v>278</v>
-      </c>
-      <c r="B190" t="s">
-        <v>416</v>
-      </c>
-      <c r="C190" s="22" t="s">
-        <v>789</v>
-      </c>
-      <c r="D190" t="s">
-        <v>436</v>
-      </c>
-      <c r="E190" s="22" t="s">
-        <v>788</v>
-      </c>
-      <c r="F190" t="s">
-        <v>143</v>
-      </c>
-      <c r="G190" t="s">
-        <v>143</v>
-      </c>
-      <c r="I190" s="12">
-        <v>1</v>
-      </c>
-      <c r="J190" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_p_art_a</v>
-      </c>
-      <c r="AJ190" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="191" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
-        <v>278</v>
-      </c>
-      <c r="B191" t="s">
-        <v>416</v>
-      </c>
-      <c r="C191" s="22" t="s">
-        <v>791</v>
-      </c>
-      <c r="D191" t="s">
-        <v>436</v>
-      </c>
-      <c r="E191" s="22" t="s">
-        <v>790</v>
-      </c>
-      <c r="F191" t="s">
-        <v>143</v>
-      </c>
-      <c r="G191" t="s">
-        <v>143</v>
-      </c>
-      <c r="I191" s="12">
-        <v>1</v>
-      </c>
-      <c r="J191" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",1,K188:AAB188)</f>
         <v>tb_p_art_n</v>
       </c>
-      <c r="AJ191" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="192" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
-        <v>278</v>
-      </c>
-      <c r="B192" t="s">
-        <v>416</v>
-      </c>
-      <c r="C192" s="22" t="s">
-        <v>793</v>
-      </c>
-      <c r="D192" t="s">
-        <v>436</v>
-      </c>
-      <c r="E192" s="22" t="s">
-        <v>792</v>
-      </c>
-      <c r="F192" t="s">
-        <v>143</v>
-      </c>
-      <c r="G192" t="s">
-        <v>143</v>
-      </c>
-      <c r="I192" s="12">
-        <v>1</v>
-      </c>
-      <c r="J192" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_p_art_n</v>
-      </c>
-      <c r="AJ192" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="193" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A193" t="s">
-        <v>278</v>
-      </c>
-      <c r="B193" t="s">
-        <v>416</v>
-      </c>
-      <c r="C193" s="22" t="s">
-        <v>795</v>
-      </c>
-      <c r="D193" t="s">
-        <v>436</v>
-      </c>
-      <c r="E193" s="22" t="s">
-        <v>794</v>
-      </c>
-      <c r="F193" t="s">
-        <v>143</v>
-      </c>
-      <c r="G193" t="s">
-        <v>143</v>
-      </c>
-      <c r="I193" s="12">
-        <v>1</v>
-      </c>
-      <c r="J193" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_n_art_a</v>
-      </c>
-      <c r="AJ193" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="194" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A194" t="s">
-        <v>278</v>
-      </c>
-      <c r="B194" t="s">
-        <v>416</v>
-      </c>
-      <c r="C194" s="22" t="s">
-        <v>797</v>
-      </c>
-      <c r="D194" t="s">
-        <v>436</v>
-      </c>
-      <c r="E194" s="22" t="s">
-        <v>796</v>
-      </c>
-      <c r="F194" t="s">
-        <v>143</v>
-      </c>
-      <c r="G194" t="s">
-        <v>143</v>
-      </c>
-      <c r="I194" s="12">
-        <v>1</v>
-      </c>
-      <c r="J194" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_n_art_a</v>
-      </c>
-      <c r="AJ194" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="195" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A195" t="s">
-        <v>278</v>
-      </c>
-      <c r="B195" t="s">
-        <v>416</v>
-      </c>
-      <c r="C195" s="22" t="s">
-        <v>799</v>
-      </c>
-      <c r="D195" t="s">
-        <v>436</v>
-      </c>
-      <c r="E195" s="22" t="s">
-        <v>798</v>
-      </c>
-      <c r="F195" t="s">
-        <v>143</v>
-      </c>
-      <c r="G195" t="s">
-        <v>143</v>
-      </c>
-      <c r="I195" s="12">
-        <v>1</v>
-      </c>
-      <c r="J195" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_n_art_n</v>
-      </c>
-      <c r="AJ195" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="196" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A196" t="s">
-        <v>278</v>
-      </c>
-      <c r="B196" t="s">
-        <v>416</v>
-      </c>
-      <c r="C196" s="22" t="s">
+      <c r="AH188" t="s">
         <v>801</v>
       </c>
-      <c r="D196" t="s">
-        <v>436</v>
-      </c>
-      <c r="E196" s="22" t="s">
-        <v>800</v>
-      </c>
-      <c r="F196" t="s">
-        <v>143</v>
-      </c>
-      <c r="G196" t="s">
-        <v>143</v>
-      </c>
-      <c r="I196" s="12">
-        <v>1</v>
-      </c>
-      <c r="J196" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_n_art_n</v>
-      </c>
-      <c r="AJ196" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="197" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A197" t="s">
-        <v>278</v>
-      </c>
-      <c r="B197" t="s">
-        <v>416</v>
-      </c>
-      <c r="C197" s="22" t="s">
-        <v>803</v>
-      </c>
-      <c r="D197" t="s">
-        <v>436</v>
-      </c>
-      <c r="E197" s="22" t="s">
-        <v>802</v>
-      </c>
-      <c r="F197" t="s">
-        <v>143</v>
-      </c>
-      <c r="G197" t="s">
-        <v>143</v>
-      </c>
-      <c r="I197" s="12">
-        <v>1</v>
-      </c>
-      <c r="J197" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_p_art_a</v>
-      </c>
-      <c r="AJ197" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="198" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A198" t="s">
-        <v>278</v>
-      </c>
-      <c r="B198" t="s">
-        <v>416</v>
-      </c>
-      <c r="C198" s="22" t="s">
-        <v>805</v>
-      </c>
-      <c r="D198" t="s">
-        <v>436</v>
-      </c>
-      <c r="E198" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="F198" t="s">
-        <v>143</v>
-      </c>
-      <c r="G198" t="s">
-        <v>143</v>
-      </c>
-      <c r="I198" s="12">
-        <v>1</v>
-      </c>
-      <c r="J198" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_p_art_a</v>
-      </c>
-      <c r="AJ198" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="199" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A199" t="s">
-        <v>278</v>
-      </c>
-      <c r="B199" t="s">
-        <v>416</v>
-      </c>
-      <c r="C199" s="22" t="s">
-        <v>807</v>
-      </c>
-      <c r="D199" t="s">
-        <v>436</v>
-      </c>
-      <c r="E199" s="22" t="s">
-        <v>806</v>
-      </c>
-      <c r="F199" t="s">
-        <v>143</v>
-      </c>
-      <c r="G199" t="s">
-        <v>143</v>
-      </c>
-      <c r="I199" s="12">
-        <v>1</v>
-      </c>
-      <c r="J199" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_p_art_n</v>
-      </c>
-      <c r="AJ199" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="200" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A200" t="s">
-        <v>278</v>
-      </c>
-      <c r="B200" t="s">
-        <v>416</v>
-      </c>
-      <c r="C200" s="22" t="s">
-        <v>809</v>
-      </c>
-      <c r="D200" t="s">
-        <v>436</v>
-      </c>
-      <c r="E200" s="22" t="s">
-        <v>808</v>
-      </c>
-      <c r="F200" t="s">
-        <v>143</v>
-      </c>
-      <c r="G200" t="s">
-        <v>143</v>
-      </c>
-      <c r="I200" s="12">
-        <v>1</v>
-      </c>
-      <c r="J200" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>tb_p_art_n</v>
-      </c>
-      <c r="AJ200" t="s">
-        <v>814</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AH184" xr:uid="{F5070472-BD41-FC47-BC46-FB0AD4499DE3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:Y66">
+  <autoFilter ref="A1:AF188" xr:uid="{F5070472-BD41-FC47-BC46-FB0AD4499DE3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:W66">
     <sortCondition ref="H4:H66"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -19064,201 +17788,201 @@
   <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="21"/>
+    <col min="1" max="1" width="30.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>695</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>697</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>699</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
+        <v>701</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>703</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
+        <v>705</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="B1" s="20" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>708</v>
       </c>
-      <c r="B2" s="20" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="19" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>710</v>
       </c>
-      <c r="B3" s="20" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="19" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>712</v>
       </c>
-      <c r="B4" s="20" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="19" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="B11" s="19" t="s">
         <v>714</v>
       </c>
-      <c r="B5" s="20" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="19" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>716</v>
       </c>
-      <c r="B6" s="20" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="19" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>718</v>
       </c>
-      <c r="B7" s="20" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="19" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
+      <c r="B14" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="B8" s="20" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>722</v>
       </c>
-      <c r="B9" s="20" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="19" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
+      <c r="B16" s="19" t="s">
         <v>724</v>
       </c>
-      <c r="B10" s="20" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="19" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>726</v>
       </c>
-      <c r="B11" s="20" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="19" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+      <c r="B18" s="19" t="s">
         <v>728</v>
       </c>
-      <c r="B12" s="20" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="20" t="s">
+      <c r="B19" s="19" t="s">
         <v>730</v>
       </c>
-      <c r="B13" s="20" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="20" t="s">
+      <c r="B20" s="19" t="s">
         <v>732</v>
       </c>
-      <c r="B14" s="20" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="19" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
+      <c r="B21" s="19" t="s">
         <v>734</v>
       </c>
-      <c r="B15" s="20" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="19" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="B22" s="19" t="s">
         <v>736</v>
       </c>
-      <c r="B16" s="20" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="19" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="B23" s="19" t="s">
         <v>738</v>
       </c>
-      <c r="B17" s="20" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="19" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="B24" s="19" t="s">
         <v>740</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
-        <v>742</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
-        <v>744</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
-        <v>746</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
-        <v>748</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
-        <v>750</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
-        <v>752</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>753</v>
       </c>
     </row>
   </sheetData>
